--- a/data/preseason2026/tpbl_summary.xlsx
+++ b/data/preseason2026/tpbl_summary.xlsx
@@ -14,79 +14,100 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="76">
   <si>
+    <t>2026-2027 賽季 TPBL 季前熱身賽 7隊戰力與綜合評分總表 (全7場核定版)</t>
+  </si>
+  <si>
     <t>2026-2027 賽季 TPBL 季前熱身賽主力球員：球權使用率 (USG%) vs 真實命中率 (TS%) 核心效率對比與象限深度解讀</t>
   </si>
   <si>
+    <t>註：採計TPBL官方熱身賽逐球電子紀錄攻守數據與四要素指標。全7場賽事實體內容核實。海神與特攻因G1打進延長賽，團隊上場時間為505分鐘。</t>
+  </si>
+  <si>
     <t>註：篩選條件為熱身賽主力出賽球員，氣泡大小依單場綜合表現值 (GmSc) 等比縮放。</t>
   </si>
   <si>
-    <t>2026-2027 賽季 TPBL 季前熱身賽 7隊戰力與綜合評分總表 (全7場核定版)</t>
-  </si>
-  <si>
     <t>【四大象限深度解讀與戰術定位 (Quadrant Analysis &amp; Tactical Roles)】</t>
   </si>
   <si>
-    <t>註：採計TPBL官方熱身賽逐球電子紀錄攻守數據與四要素指標。全7場賽事實體內容核實。海神與特攻因G1打進延長賽，團隊上場時間為505分鐘。</t>
-  </si>
-  <si>
     <t>【區塊 A：團隊四大要素與進階數據指標 (Team Four Factors &amp; Advanced Metrics)】</t>
   </si>
   <si>
     <t>象限分組</t>
   </si>
   <si>
+    <t>球隊名稱</t>
+  </si>
+  <si>
     <t>代表球員與數據</t>
   </si>
   <si>
     <t>核心特徵與戰術價值分析</t>
   </si>
   <si>
+    <t>出賽場次</t>
+  </si>
+  <si>
     <t>熱身賽攻防影響力評估</t>
   </si>
   <si>
-    <t>球隊名稱</t>
-  </si>
-  <si>
-    <t>出賽場次</t>
+    <t>戰績</t>
+  </si>
+  <si>
+    <t>團隊上場時間[分]</t>
+  </si>
+  <si>
+    <t>團隊總得分</t>
+  </si>
+  <si>
+    <t>團隊總出手</t>
   </si>
   <si>
     <t>第一象限：高球權・高效率 (核心進攻支柱)</t>
   </si>
   <si>
-    <t>戰績</t>
-  </si>
-  <si>
-    <t>團隊上場時間[分]</t>
-  </si>
-  <si>
-    <t>團隊總得分</t>
+    <t>團隊命中率%</t>
+  </si>
+  <si>
+    <t>團隊三分出手比 (Team 3PAr)</t>
+  </si>
+  <si>
+    <t>團隊有效命中率 (Team eFG%)</t>
+  </si>
+  <si>
+    <t>團隊回合數 (Possessions)</t>
+  </si>
+  <si>
+    <t>比賽節奏 (Pace, 48分)</t>
+  </si>
+  <si>
+    <t>百回合進攻效率 (ORtg)</t>
+  </si>
+  <si>
+    <t>團隊失誤率 (Team TOV%)</t>
   </si>
   <si>
     <t>洛斯柯 (USG% 32.4%, TS% 69.6%, GmSc 29.2)、麥基 (USG% 28.5%, TS% 68.0%, GmSc 16.6)、克雷格 (USG% 32.3%, TS% 67.8%, GmSc 17.3)、林俊吉 (USG% 33.6%, TS% 75.5%, GmSc 14.8)、莫騰 (USG% 27.9%, TS% 63.4%, GmSc 21.5)、沃許本 (USG% 27.6%, TS% 64.2%, GmSc 20.6)</t>
   </si>
   <si>
-    <t>團隊總出手</t>
-  </si>
-  <si>
     <t>具備強大個人硬解與創造機會能力，在大量持球負擔下仍能維持優於聯盟平均之真實命中率，是球隊關鍵時刻的第一選擇。</t>
   </si>
   <si>
     <t>洛斯柯狂轟64分展現MVP身手；麥基五外砲火轟跨對手；林俊吉下半場爆發獨得23分率隊逆轉；莫騰狂轟52分展現得分王實力。</t>
   </si>
   <si>
-    <t>團隊命中率%</t>
+    <t>臺北台新戰神</t>
   </si>
   <si>
     <t>第二象限：低球權・高效率 (高效終結與空檔奇兵)</t>
   </si>
   <si>
-    <t>團隊三分出手比 (Team 3PAr)</t>
+    <t>2場</t>
   </si>
   <si>
     <t>辛巴 (USG% 18.2%, TS% 87.9%, GmSc 10.3)、王皓吉 (USG% 11.8%, TS% 84.5%, GmSc 6.1)、蘇文儒 (USG% 16.0%, TS% 80.5%, GmSc 12.3)、杭特 (USG% 24.5%, TS% 67.8%, GmSc 15.8)、謝亞軒 (USG% 20.9%, TS% 47.0%, GmSc 12.3)</t>
   </si>
   <si>
-    <t>團隊有效命中率 (Team eFG%)</t>
+    <t>2勝0敗</t>
   </si>
   <si>
     <t>不佔用過多球權，主要透過無球空切、空檔接應投射或進攻籃板補籃得分，得分產出效率極其驚人。</t>
@@ -95,27 +116,15 @@
     <t>王皓吉外線3中2繳超高真實命中率；辛巴禁區命中率高達9成；蘇文儒外線火力凶猛，為二陣提供強大火力支援。</t>
   </si>
   <si>
-    <t>團隊回合數 (Possessions)</t>
-  </si>
-  <si>
-    <t>比賽節奏 (Pace, 48分)</t>
-  </si>
-  <si>
     <t>第三象限：低球權・低效率 (體系角色調整中)</t>
   </si>
   <si>
-    <t>百回合進攻效率 (ORtg)</t>
-  </si>
-  <si>
     <t>莊博元 (USG% 10.7%, TS% 41.4%, GmSc 3.9)、盧冠軒 (USG% 21.8%, TS% 35.3%, GmSc 4.9)、黃聰翰 (USG% 18.3%, TS% 18.4%, GmSc -2.9)</t>
   </si>
   <si>
     <t>球權佔比低於聯盟平均，外線手感尚未回溫，主要在防守與輪替端提供支援。</t>
   </si>
   <si>
-    <t>團隊失誤率 (Team TOV%)</t>
-  </si>
-  <si>
     <t>射手手感普遍冰冷，外圍投射把握度待調整，需盡快適應戰術體系與出賽節奏。</t>
   </si>
   <si>
@@ -125,19 +134,10 @@
     <t>肯刀爾 (USG% 30.3%, TS% 43.8%, GmSc 9.7)、高錦瑋 (USG% 21.4%, TS% 50.0%, GmSc 5.4)、曹薰襄 (USG% 18.0%, TS% 39.7%, GmSc 5.4)</t>
   </si>
   <si>
-    <t>臺北台新戰神</t>
-  </si>
-  <si>
     <t>承擔球隊極大量攻堅與終結責任，但因遭遇對手重點包夾或自身外線手感起伏，真實命中率略低於聯盟平均。</t>
   </si>
   <si>
     <t>肯刀爾持球強攻造犯規但外線手感欠佳；高錦瑋與曹薰襄扛起雲豹後場組織，失誤控制與終結穩定度為開季微調重點。</t>
-  </si>
-  <si>
-    <t>2場</t>
-  </si>
-  <si>
-    <t>2勝0敗</t>
   </si>
   <si>
     <t>新北國王</t>
@@ -390,11 +390,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="3">
-    <tableStyle count="2" pivot="0" name="核心球員效率圖與象限解讀-style">
+    <tableStyle count="2" pivot="0" name="7隊戰力與綜合評分-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="7隊戰力與綜合評分-style">
+    <tableStyle count="2" pivot="0" name="核心球員效率圖與象限解讀-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
@@ -419,7 +419,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A6:M12" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A6:M12" displayName="Table_1" name="Table_1" id="2">
   <tableColumns count="13">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A7:D10" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A7:D10" displayName="Table_2" name="Table_2" id="1">
   <tableColumns count="4">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -674,12 +674,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -701,54 +701,54 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="M5" s="5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D6" s="6">
         <v>480.0</v>
@@ -786,10 +786,10 @@
         <v>42</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D7" s="6">
         <v>480.0</v>
@@ -827,7 +827,7 @@
         <v>43</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>44</v>
@@ -868,7 +868,7 @@
         <v>45</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>44</v>
@@ -909,7 +909,7 @@
         <v>46</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>44</v>
@@ -950,7 +950,7 @@
         <v>47</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>48</v>
@@ -991,7 +991,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>48</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>51</v>
@@ -1055,10 +1055,10 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>55</v>
@@ -1075,7 +1075,7 @@
         <v>42</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>58</v>
@@ -1198,17 +1198,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1219,69 +1219,69 @@
         <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
